--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48524,7 +48524,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49316,7 +49316,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50900,7 +50900,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51692,7 +51692,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52484,7 +52484,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -53276,7 +53276,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54068,7 +54068,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56444,7 +56444,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57236,7 +57236,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48524,7 +48524,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49316,7 +49316,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50900,7 +50900,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51692,7 +51692,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52484,7 +52484,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -53276,7 +53276,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54068,7 +54068,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54860,7 +54860,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55652,7 +55652,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56444,7 +56444,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57236,7 +57236,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>907</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>3.523179628050896</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>43</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.7776314142836784</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>931</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>3.616405990865914</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>33</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.5967868993339858</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>1046</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>4.06311564602121</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>40</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.7233780597987707</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>849</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>3.297882584581268</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>34</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.6148713508289551</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>846</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>3.286229289229391</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>35</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.6329558023239243</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>940</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>3.651365876921545</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>28</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.5063646418591394</v>
       </c>
@@ -5913,9 +5877,6 @@
       <c r="O28" t="n">
         <v>30</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.542533544849078</v>
       </c>
@@ -6309,9 +6270,6 @@
       <c r="O30" t="n">
         <v>1016</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>3.946582692502437</v>
       </c>
@@ -6705,9 +6663,6 @@
       <c r="O32" t="n">
         <v>36</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.6510402538188936</v>
       </c>
@@ -7101,9 +7056,6 @@
       <c r="O34" t="n">
         <v>1130</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>4.389407915873774</v>
       </c>
@@ -7497,9 +7449,6 @@
       <c r="O36" t="n">
         <v>50</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.9042225747484635</v>
       </c>
@@ -7893,9 +7842,6 @@
       <c r="O38" t="n">
         <v>1134</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>4.40494564300961</v>
       </c>
@@ -8289,9 +8235,6 @@
       <c r="O40" t="n">
         <v>36</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.6510402538188936</v>
       </c>
@@ -8685,9 +8628,6 @@
       <c r="O42" t="n">
         <v>1187</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>4.610820527559442</v>
       </c>
@@ -9081,9 +9021,6 @@
       <c r="O44" t="n">
         <v>34</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.6148713508289551</v>
       </c>
@@ -9477,9 +9414,6 @@
       <c r="O46" t="n">
         <v>1315</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>5.108027795906205</v>
       </c>
@@ -9873,9 +9807,6 @@
       <c r="O48" t="n">
         <v>53</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.9584759292333711</v>
       </c>
@@ -10269,9 +10200,6 @@
       <c r="O50" t="n">
         <v>1124</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>4.330335648207231</v>
       </c>
@@ -10665,9 +10593,6 @@
       <c r="O52" t="n">
         <v>41</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.7399286239583475</v>
       </c>
@@ -11061,9 +10986,6 @@
       <c r="O54" t="n">
         <v>1181</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>4.549934520046921</v>
       </c>
@@ -11457,9 +11379,6 @@
       <c r="O56" t="n">
         <v>44</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.794069742784568</v>
       </c>
@@ -11853,9 +11772,6 @@
       <c r="O58" t="n">
         <v>1495</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>5.759654621058549</v>
       </c>
@@ -12249,9 +12165,6 @@
       <c r="O60" t="n">
         <v>34</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.6135993466971662</v>
       </c>
@@ -12645,9 +12558,6 @@
       <c r="O62" t="n">
         <v>1525</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>5.875232974658386</v>
       </c>
@@ -13041,9 +12951,6 @@
       <c r="O64" t="n">
         <v>52</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.9384460596544895</v>
       </c>
@@ -13437,9 +13344,6 @@
       <c r="O66" t="n">
         <v>1641</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>6.32213594191109</v>
       </c>
@@ -13833,9 +13737,6 @@
       <c r="O68" t="n">
         <v>43</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.7760227031758279</v>
       </c>
@@ -14229,9 +14130,6 @@
       <c r="O70" t="n">
         <v>1460</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>5.624813208525405</v>
       </c>
@@ -14625,9 +14523,6 @@
       <c r="O72" t="n">
         <v>41</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.7399286239583475</v>
       </c>
@@ -15021,9 +14916,6 @@
       <c r="O74" t="n">
         <v>1548</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>5.963843045751595</v>
       </c>
@@ -15417,9 +15309,6 @@
       <c r="O76" t="n">
         <v>45</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.8121167823933082</v>
       </c>
@@ -15813,9 +15702,6 @@
       <c r="O78" t="n">
         <v>1637</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>6.306725494764446</v>
       </c>
@@ -16209,9 +16095,6 @@
       <c r="O80" t="n">
         <v>52</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.9384460596544895</v>
       </c>
@@ -16605,9 +16488,6 @@
       <c r="O82" t="n">
         <v>1572</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>6.056305728631465</v>
       </c>
@@ -17001,9 +16881,6 @@
       <c r="O84" t="n">
         <v>38</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.6857875051321268</v>
       </c>
@@ -17397,9 +17274,6 @@
       <c r="O86" t="n">
         <v>1680</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>6.472387801590878</v>
       </c>
@@ -17793,9 +17667,6 @@
       <c r="O88" t="n">
         <v>52</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.9384460596544895</v>
       </c>
@@ -18189,9 +18060,6 @@
       <c r="O90" t="n">
         <v>1698</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>6.54173481375078</v>
       </c>
@@ -18585,9 +18453,6 @@
       <c r="O92" t="n">
         <v>42</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.7579756635670877</v>
       </c>
@@ -18981,9 +18846,6 @@
       <c r="O94" t="n">
         <v>1656</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>6.379925118711008</v>
       </c>
@@ -19377,9 +19239,6 @@
       <c r="O96" t="n">
         <v>33</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.595552307088426</v>
       </c>
@@ -19773,9 +19632,6 @@
       <c r="O98" t="n">
         <v>1309</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>4.995995474902861</v>
       </c>
@@ -20169,9 +20025,6 @@
       <c r="O100" t="n">
         <v>38</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.6823120827235168</v>
       </c>
@@ -20565,9 +20418,6 @@
       <c r="O102" t="n">
         <v>1414</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>5.396743775028759</v>
       </c>
@@ -20961,9 +20811,6 @@
       <c r="O104" t="n">
         <v>34</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.6104897582263046</v>
       </c>
@@ -21357,9 +21204,6 @@
       <c r="O106" t="n">
         <v>1634</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>6.23640688005445</v>
       </c>
@@ -21753,9 +21597,6 @@
       <c r="O108" t="n">
         <v>36</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.6464009204749108</v>
       </c>
@@ -22149,9 +21990,6 @@
       <c r="O110" t="n">
         <v>1269</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>4.843329455807281</v>
       </c>
@@ -22545,9 +22383,6 @@
       <c r="O112" t="n">
         <v>25</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.4488895281075769</v>
       </c>
@@ -22941,9 +22776,6 @@
       <c r="O114" t="n">
         <v>1516</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>5.786042123722488</v>
       </c>
@@ -23337,9 +23169,6 @@
       <c r="O116" t="n">
         <v>53</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.9516457995880631</v>
       </c>
@@ -23733,9 +23562,6 @@
       <c r="O118" t="n">
         <v>1318</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>5.030345329199367</v>
       </c>
@@ -24129,9 +23955,6 @@
       <c r="O120" t="n">
         <v>47</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.8439123128422447</v>
       </c>
@@ -24525,9 +24348,6 @@
       <c r="O122" t="n">
         <v>1498</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>5.717342415129477</v>
       </c>
@@ -24921,9 +24741,6 @@
       <c r="O124" t="n">
         <v>41</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.7361788260964262</v>
       </c>
@@ -25317,9 +25134,6 @@
       <c r="O126" t="n">
         <v>1705</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>6.507389063949105</v>
       </c>
@@ -25713,9 +25527,6 @@
       <c r="O128" t="n">
         <v>42</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.7541344072207292</v>
       </c>
@@ -26109,9 +25920,6 @@
       <c r="O130" t="n">
         <v>1518</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>5.793675424677267</v>
       </c>
@@ -26505,9 +26313,6 @@
       <c r="O132" t="n">
         <v>32</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.5745785959776984</v>
       </c>
@@ -26901,9 +26706,6 @@
       <c r="O134" t="n">
         <v>1675</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>6.392889549627419</v>
       </c>
@@ -27297,9 +27099,6 @@
       <c r="O136" t="n">
         <v>41</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.7361788260964262</v>
       </c>
@@ -27693,9 +27492,6 @@
       <c r="O138" t="n">
         <v>1687</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>6.438689355356094</v>
       </c>
@@ -28089,9 +27885,6 @@
       <c r="O140" t="n">
         <v>35</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.6284453393506078</v>
       </c>
@@ -28485,9 +28278,6 @@
       <c r="O142" t="n">
         <v>1594</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>6.08374086095887</v>
       </c>
@@ -28881,9 +28671,6 @@
       <c r="O144" t="n">
         <v>41</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.7361788260964262</v>
       </c>
@@ -29277,9 +29064,6 @@
       <c r="O146" t="n">
         <v>1439</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>5.440222502453961</v>
       </c>
@@ -29673,9 +29457,6 @@
       <c r="O148" t="n">
         <v>54</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.9640816216495597</v>
       </c>
@@ -30069,9 +29850,6 @@
       <c r="O150" t="n">
         <v>1484</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>5.610347598083167</v>
       </c>
@@ -30465,9 +30243,6 @@
       <c r="O152" t="n">
         <v>45</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.8034013513746332</v>
       </c>
@@ -30861,9 +30636,6 @@
       <c r="O154" t="n">
         <v>1492</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>5.640592059528359</v>
       </c>
@@ -31257,9 +31029,6 @@
       <c r="O156" t="n">
         <v>62</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>1.106908528560606</v>
       </c>
@@ -31653,9 +31422,6 @@
       <c r="O158" t="n">
         <v>1330</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>5.028141715263216</v>
       </c>
@@ -32049,9 +31815,6 @@
       <c r="O160" t="n">
         <v>40</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.7141345345552295</v>
       </c>
@@ -32445,9 +32208,6 @@
       <c r="O162" t="n">
         <v>1488</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>5.625469828805763</v>
       </c>
@@ -32841,9 +32601,6 @@
       <c r="O164" t="n">
         <v>46</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.8212547147385139</v>
       </c>
@@ -33237,9 +32994,6 @@
       <c r="O166" t="n">
         <v>1473</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>5.568761463596027</v>
       </c>
@@ -33633,9 +33387,6 @@
       <c r="O168" t="n">
         <v>45</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.8034013513746332</v>
       </c>
@@ -34029,9 +33780,6 @@
       <c r="O170" t="n">
         <v>1566</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>5.920353327896387</v>
       </c>
@@ -34425,9 +34173,6 @@
       <c r="O172" t="n">
         <v>65</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>1.160468618652248</v>
       </c>
@@ -34821,9 +34566,6 @@
       <c r="O174" t="n">
         <v>1622</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>6.132064558012734</v>
       </c>
@@ -35217,9 +34959,6 @@
       <c r="O176" t="n">
         <v>66</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>1.178321982016129</v>
       </c>
@@ -35613,9 +35352,6 @@
       <c r="O178" t="n">
         <v>1542</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>5.82961994356081</v>
       </c>
@@ -36009,9 +35745,6 @@
       <c r="O180" t="n">
         <v>58</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>1.035495075105083</v>
       </c>
@@ -36405,9 +36138,6 @@
       <c r="O182" t="n">
         <v>1727</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>6.529023114480881</v>
       </c>
@@ -36801,9 +36531,6 @@
       <c r="O184" t="n">
         <v>59</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>1.053348438468963</v>
       </c>
@@ -37197,9 +36924,6 @@
       <c r="O186" t="n">
         <v>1763</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>6.665123190984247</v>
       </c>
@@ -37593,9 +37317,6 @@
       <c r="O188" t="n">
         <v>42</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.7498412612829909</v>
       </c>
@@ -37989,9 +37710,6 @@
       <c r="O190" t="n">
         <v>1536</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>5.806936597476916</v>
       </c>
@@ -38385,9 +38103,6 @@
       <c r="O192" t="n">
         <v>21</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.3749206306414954</v>
       </c>
@@ -38781,9 +38496,6 @@
       <c r="O194" t="n">
         <v>1824</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>6.828083713653978</v>
       </c>
@@ -39177,9 +38889,6 @@
       <c r="O196" t="n">
         <v>44</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.7832930011613209</v>
       </c>
@@ -39573,9 +39282,6 @@
       <c r="O198" t="n">
         <v>1725</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>6.457480485774733</v>
       </c>
@@ -39969,9 +39675,6 @@
       <c r="O200" t="n">
         <v>49</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.8723035694751073</v>
       </c>
@@ -40365,9 +40068,6 @@
       <c r="O202" t="n">
         <v>1793</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>6.712036238257446</v>
       </c>
@@ -40761,9 +40461,6 @@
       <c r="O204" t="n">
         <v>38</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.6764803191847771</v>
       </c>
@@ -41157,9 +40854,6 @@
       <c r="O206" t="n">
         <v>1625</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>6.083133790947211</v>
       </c>
@@ -41553,9 +41247,6 @@
       <c r="O208" t="n">
         <v>34</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.6052718645337479</v>
       </c>
@@ -41949,9 +41640,6 @@
       <c r="O210" t="n">
         <v>1943</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>7.273556280498727</v>
       </c>
@@ -42345,9 +42033,6 @@
       <c r="O212" t="n">
         <v>62</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>1.103731047090952</v>
       </c>
@@ -42741,9 +42426,6 @@
       <c r="O214" t="n">
         <v>1734</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>6.491171688309209</v>
       </c>
@@ -43137,9 +42819,6 @@
       <c r="O216" t="n">
         <v>42</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.7476887738358063</v>
       </c>
@@ -43533,9 +43212,6 @@
       <c r="O218" t="n">
         <v>1972</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>7.382116821998708</v>
       </c>
@@ -43929,9 +43605,6 @@
       <c r="O220" t="n">
         <v>58</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>1.032522592439923</v>
       </c>
@@ -44325,9 +43998,6 @@
       <c r="O222" t="n">
         <v>2032</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>7.606724838895221</v>
       </c>
@@ -44721,9 +44391,6 @@
       <c r="O224" t="n">
         <v>54</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.9613141377888939</v>
       </c>
@@ -45117,9 +44784,6 @@
       <c r="O226" t="n">
         <v>1872</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>7.007770127171187</v>
       </c>
@@ -45513,9 +45177,6 @@
       <c r="O228" t="n">
         <v>55</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.9791162514516512</v>
       </c>
@@ -45909,9 +45570,6 @@
       <c r="O230" t="n">
         <v>2154</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>8.063427806584796</v>
       </c>
@@ -46305,9 +45963,6 @@
       <c r="O232" t="n">
         <v>62</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>1.103731047090952</v>
       </c>
@@ -46701,9 +46356,6 @@
       <c r="O234" t="n">
         <v>1906</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>7.135048003412544</v>
       </c>
@@ -47097,9 +46749,6 @@
       <c r="O236" t="n">
         <v>50</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.8901056831378646</v>
       </c>
@@ -47493,9 +47142,6 @@
       <c r="O238" t="n">
         <v>1798</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>6.730753572998822</v>
       </c>
@@ -47889,9 +47535,6 @@
       <c r="O240" t="n">
         <v>41</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.7298866601730489</v>
       </c>
@@ -48285,9 +47928,6 @@
       <c r="O242" t="n">
         <v>1946</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>7.214347609808042</v>
       </c>
@@ -48681,9 +48321,6 @@
       <c r="O244" t="n">
         <v>48</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.853586829653144</v>
       </c>
@@ -49077,9 +48714,6 @@
       <c r="O246" t="n">
         <v>1817</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>6.736109767225701</v>
       </c>
@@ -49473,9 +49107,6 @@
       <c r="O248" t="n">
         <v>40</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.7113223580442867</v>
       </c>
@@ -49869,9 +49500,6 @@
       <c r="O250" t="n">
         <v>1956</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>7.251420310783418</v>
       </c>
@@ -50265,9 +49893,6 @@
       <c r="O252" t="n">
         <v>71</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>1.262597185528609</v>
       </c>
@@ -50661,9 +50286,6 @@
       <c r="O254" t="n">
         <v>1912</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>7.088300426491767</v>
       </c>
@@ -51057,9 +50679,6 @@
       <c r="O256" t="n">
         <v>50</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.8891529475553585</v>
       </c>
@@ -51453,9 +51072,6 @@
       <c r="O258" t="n">
         <v>2017</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>7.477563786733207</v>
       </c>
@@ -51849,9 +51465,6 @@
       <c r="O260" t="n">
         <v>45</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.8002376527998226</v>
       </c>
@@ -52245,9 +51858,6 @@
       <c r="O262" t="n">
         <v>1851</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>6.862156950541977</v>
       </c>
@@ -52641,9 +52251,6 @@
       <c r="O264" t="n">
         <v>58</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>1.031417419164216</v>
       </c>
@@ -53037,9 +52644,6 @@
       <c r="O266" t="n">
         <v>2022</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>7.496100137220895</v>
       </c>
@@ -53433,9 +53037,6 @@
       <c r="O268" t="n">
         <v>47</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0.8358037707020369</v>
       </c>
@@ -53829,9 +53430,6 @@
       <c r="O270" t="n">
         <v>2008</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>7.444198355855369</v>
       </c>
@@ -54225,9 +53823,6 @@
       <c r="O272" t="n">
         <v>66</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>1.173681890773073</v>
       </c>
@@ -54621,9 +54216,6 @@
       <c r="O274" t="n">
         <v>1980</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>7.340394793124319</v>
       </c>
@@ -55017,9 +54609,6 @@
       <c r="O276" t="n">
         <v>49</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.8713698886042514</v>
       </c>
@@ -55413,9 +55002,6 @@
       <c r="O278" t="n">
         <v>2044</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>7.577660079366722</v>
       </c>
@@ -55809,9 +55395,6 @@
       <c r="O280" t="n">
         <v>52</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.9247190654575728</v>
       </c>
@@ -56205,9 +55788,6 @@
       <c r="O282" t="n">
         <v>1835</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>6.802840628981377</v>
       </c>
@@ -56601,9 +56181,6 @@
       <c r="O284" t="n">
         <v>58</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>1.031417419164216</v>
       </c>
@@ -56997,9 +56574,6 @@
       <c r="O286" t="n">
         <v>1522</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>5.642465088452128</v>
       </c>
@@ -57392,9 +56966,6 @@
       </c>
       <c r="O288" t="n">
         <v>49</v>
-      </c>
-      <c r="Q288" t="n">
-        <v>0</v>
       </c>
       <c r="R288" t="n">
         <v>0.8713698886042514</v>

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15162,7 +15162,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19878,7 +19878,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30882,7 +30882,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31668,7 +31668,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33240,7 +33240,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34026,7 +34026,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34812,7 +34812,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35598,7 +35598,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36384,7 +36384,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37170,7 +37170,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37956,7 +37956,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38742,7 +38742,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41100,7 +41100,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41886,7 +41886,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42672,7 +42672,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43458,7 +43458,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45030,7 +45030,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45816,7 +45816,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46602,7 +46602,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47388,7 +47388,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48174,7 +48174,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48960,7 +48960,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -50532,7 +50532,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -51318,7 +51318,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -52104,7 +52104,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52890,7 +52890,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53676,7 +53676,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -54462,7 +54462,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -56034,7 +56034,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -56820,7 +56820,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25370,7 +25370,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41090,7 +41090,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42662,7 +42662,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44234,7 +44234,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47378,7 +47378,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48164,7 +48164,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48950,7 +48950,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50522,7 +50522,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51308,7 +51308,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -53666,7 +53666,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54452,7 +54452,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56024,7 +56024,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56810,7 +56810,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25370,7 +25370,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41090,7 +41090,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42662,7 +42662,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44234,7 +44234,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47378,7 +47378,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48164,7 +48164,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48950,7 +48950,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50522,7 +50522,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51308,7 +51308,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -53666,7 +53666,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54452,7 +54452,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56024,7 +56024,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56810,7 +56810,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25370,7 +25370,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41090,7 +41090,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42662,7 +42662,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44234,7 +44234,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47378,7 +47378,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48164,7 +48164,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48950,7 +48950,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50522,7 +50522,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51308,7 +51308,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -53666,7 +53666,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54452,7 +54452,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56024,7 +56024,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56810,7 +56810,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">

--- a/diseases/d213/2020-2025.xlsx
+++ b/diseases/d213/2020-2025.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19868,7 +19868,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25370,7 +25370,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30872,7 +30872,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31658,7 +31658,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34016,7 +34016,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40304,7 +40304,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41090,7 +41090,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41876,7 +41876,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42662,7 +42662,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44234,7 +44234,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45806,7 +45806,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46592,7 +46592,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47378,7 +47378,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48164,7 +48164,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48950,7 +48950,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -50522,7 +50522,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -51308,7 +51308,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -53666,7 +53666,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -54452,7 +54452,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -56024,7 +56024,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -56810,7 +56810,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
